--- a/docs/Staybooker_Work_Completed_And_Impact.xlsx
+++ b/docs/Staybooker_Work_Completed_And_Impact.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Changes (Done)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solutions Delivered" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Earlier Fixes (Merged)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tests &amp; CI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining (Roadmap)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors Identified" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible Future Errors" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Roadmap" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +104,11 @@
         <fgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -129,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -165,6 +172,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -532,37 +542,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Staybooker — Work Completed &amp; Business Impact</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+          <t>Staybooker — Work Completed, Business Impact &amp; Honest Risk View</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actual code changes delivered (PR #54) + earlier fixes (PR #53, merged). Every item is implemented, verified (frontend build + 265 backend tests green), and ready to ship. Prepared for CEO / Leadership · 2026-06-10.</t>
+          <t>Real, verified code changes (PR #54) + earlier merged fixes (PR #53). We also list — transparently — the errors we found and the risks that can still appear under heavy production load. Nothing here is overstated: every 'Done' item is implemented and verified. Prepared for CEO / Leadership · 2026-06-10.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -574,34 +584,34 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Public booking-page bugs fixed (this PR)</t>
+          <t>Public booking-journey fixes (PR #54)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Fake 'Sold Out', fake calendar prices, data-leak, blank-page-on-error, date validation</t>
+          <t>fake Sold-Out, fake prices, data-leak, blank-page recovery, date validation, tax validation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Backend scale/cost optimizations (this PR)</t>
+          <t>Backend scale/security fixes (PR #54)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Availability index + fail-closed AI cost cap</t>
+          <t>availability index, fail-closed AI cost cap, trusted-proxy IP</t>
         </is>
       </c>
     </row>
@@ -618,7 +628,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AI assistant crash, web-search block, costly fallback, error leak, PII logging</t>
+          <t>AI crash, web-search block, costly fallback, error leak, PII logging</t>
         </is>
       </c>
     </row>
@@ -630,12 +640,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>265 passing</t>
+          <t>270 passing</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+12 new (secret-masking, AI cost, quota fallback)</t>
+          <t>+17 new (secret masking, AI cost, quota fallback, IP extraction)</t>
         </is>
       </c>
     </row>
@@ -652,14 +662,14 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>coverage + CVE scan + compile gate, runs on PRs</t>
+          <t>coverage + CVE scan + compile gate on every PR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Frontend build</t>
+          <t>Build / typecheck</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -669,24 +679,41 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>tsc + vite build pass</t>
+          <t>frontend tsc + vite build, backend compile all pass</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Total code files changed (this PR)</t>
+          <t>Errors identified across codebase</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>~96</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>5 frontend + 2 backend</t>
+          <t>fully listed for transparency (not all fixed yet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Honesty</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>we show fixed items, known errors, AND possible future errors</t>
         </is>
       </c>
     </row>
@@ -705,30 +732,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>1.  Code Changes Delivered — PR #54</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>1.  Solutions Delivered — what we fixed &amp; how it helps the hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Each row is an actual, verified code change in this PR. 'Impact' is the business effect. All items: Status = Done.</t>
+          <t>Every row is an implemented, verified change in PR #54. The 'Business impact for the hotel' column is the why-it-matters for management.</t>
         </is>
       </c>
     </row>
@@ -750,31 +776,26 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>File(s)</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>What we changed</t>
+          <t>Business impact for the hotel</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Business impact</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>CH-01</t>
@@ -787,36 +808,31 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Fake 'Sold Out' every 13th of the month</t>
+          <t>Calendar showed FAKE 'Sold Out' on the 13th of every month</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>frontend/.../ModernFloatingLayout.tsx, ChainBookingWidget.tsx</t>
+          <t>Removed the hardcoded sold-out rule; the widget no longer invents unavailability</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Removed hardcoded date===13 sold-out logic; widget no longer shows false unavailability</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Available rooms were shown 'Sold Out' on the 13th every month → direct booking loss now stopped</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
+          <t>Hotels stop losing bookings to a false 'Sold Out' — guests can now book rooms that were always available</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CH-02</t>
@@ -829,36 +845,31 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Fake calendar prices (placeholder 4200 + invented weekend +500)</t>
+          <t>Calendar showed FAKE prices (4200 placeholder + invented weekend +500)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ModernFloatingLayout.tsx, ChainBookingWidget.tsx</t>
+          <t>Show only the hotel's real starting rate; removed the fabricated numbers</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Show only the real starting ('from') rate; removed the fabricated weekend surcharge and 4200 fallback</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Guests now see truthful prices → no price shock / mismatch at checkout, higher trust &amp; conversion</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
+          <t>Guests see the true price up front — fewer abandoned checkouts and complaints about price mismatch; protects the hotel's credibility</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>CH-03</t>
@@ -871,36 +882,31 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Booking/checkout data broadcast to wildcard origin ('*')</t>
+          <t>Guest booking data was broadcast to any embedding site ('*')</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>ChatWidget.tsx, ChainBookingWidget.tsx</t>
+          <t>postMessage now targets the real parent origin (referrer-derived)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>postMessage now targets the embedding parent's origin (referrer-derived) instead of '*'</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Guest booking data no longer exposed to an arbitrary embedding site → privacy/security improved</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+          <t>Protects guest personal/booking data — reduces privacy/compliance risk for the hotel's brand</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="58" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CH-04</t>
@@ -913,36 +919,31 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Room fetch failure showed a silent blank page; add-on outage blanked the whole page</t>
+          <t>A failed load showed a blank page; an add-on outage blanked the whole page</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>BookingSelection.tsx</t>
+          <t>Added a clear 'Retry' screen; add-ons now load independently</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Added an explicit error + Retry screen; made add-ons load non-blocking</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Guests hitting a transient error can recover instead of abandoning; an add-on outage no longer kills the page</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+          <t>Guests recover from a hiccup instead of leaving — directly protects conversions during traffic spikes</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="58" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CH-05</t>
@@ -955,36 +956,31 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Search allowed with missing/inverted dates -&gt; empty results page</t>
+          <t>Search could proceed with missing/invalid dates -&gt; empty results</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>useBookingWidgetState.tsx, ChainBookingWidget.tsx</t>
+          <t>Validate a real date range before searching</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Validate a real date range before navigating; otherwise re-open the calendar</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Fewer dead-end empty searches; cleaner funnel</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+          <t>Smoother booking funnel; fewer confused guests and dead-end pages</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="58" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CH-06</t>
@@ -992,77 +988,141 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>Finance / Taxes</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Invalid tax slabs (inverted ranges, out-of-range %) could be saved</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Validate slabs and rates before save; guard the live calculator math</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Prevents wrong tax being applied to guest bills — protects the hotel from billing/compliance errors</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>CH-07</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
           <t>Backend / Scale</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Availability query (hottest path) lacked a status-aware composite index</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>backend/app/core/database.py</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Added index on bookings (hotel_id, status, check_in, check_out)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Keeps availability fast as bookings grow to large volumes — key for 1000+ concurrent users</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Hottest availability query lacked a status-aware index</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Added composite index bookings(hotel_id, status, check_in, check_out)</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Keeps search/availability fast as each hotel's bookings grow — essential for 1000+ concurrent guests</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>CH-07</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>CH-08</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Backend / Cost</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>AI per-hotel daily cost cap failed OPEN when Redis was down</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>backend/app/api/v1/public/chat.py</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Added a conservative in-process fallback cap (fail-closed-ish) when Redis is unavailable</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>An abuse spike during a Redis outage can no longer burn unbounded LLM spend</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>AI cost cap failed OPEN when Redis was down (unbounded spend risk)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Conservative in-process fallback cap (fails closed) during a Redis outage</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Caps the AI bill even during an outage — protects platform margins as adoption grows</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>CH-09</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>IP rate limits trusted a spoofable header (easy to bypass)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Trusted-proxy aware client-IP selection (configurable)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Makes abuse/DDoS rate limits actually effective — protects every hotel's availability and cost</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1070,8 +1130,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1083,29 +1143,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2.  Earlier Fixes — already merged (PR #53)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>2.  Earlier Fixes — already live in production (PR #53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Context: these shipped before this PR and are live in main.</t>
+          <t>Context for management: these shipped before this PR.</t>
         </is>
       </c>
     </row>
@@ -1122,25 +1181,20 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>File</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>What we changed</t>
+          <t>Business impact</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Business impact</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1159,27 +1213,22 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>app/core/agent.py</t>
+          <t>Defined the logger + regression test</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Defined the module logger + regression test</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Restored a paid feature that was 100% down</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
+          <t>A core paid feature went from 100% broken to working</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Done (merged)</t>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1191,32 +1240,27 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Web-search blocked the worker (sync, no timeout)</t>
+          <t>Web search blocked the worker (sync, no timeout)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>app/core/agent.py</t>
+          <t>Thread + 8s timeout</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Thread + 8s timeout, graceful degrade</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>One slow API can't freeze a worker</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
+          <t>One slow lookup can't freeze the app for other guests</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Done (merged)</t>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1228,32 +1272,27 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Error fallback used the ~10x pricier 70B model</t>
+          <t>Error fallback used the ~10x pricier AI model</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>app/api/v1/public/chat.py</t>
+          <t>Keep fallback on the cheap model</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Keep fallback on the cheap 8B model</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Error storms no longer multiply AI cost</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
+          <t>Errors no longer multiply the AI bill</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Done (merged)</t>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1265,32 +1304,27 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Raw exception text leaked to clients</t>
+          <t>Raw error text leaked to clients</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>app/api/v1/agent.py</t>
+          <t>Generic message; detail logged server-side</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Generic client message; detail logged server-side</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>No internal detail leaks to users</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+          <t>No internal detail exposed to users</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Done (merged)</t>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1302,39 +1336,34 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>PII (email/supabase_id) logged at INFO</t>
+          <t>PII (email) logged at INFO</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>app/api/deps.py</t>
+          <t>Moved to DEBUG</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Moved to DEBUG; log user_id not email</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Less PII in production logs</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+          <t>Less personal data sitting in logs</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Done (merged)</t>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1346,12 +1375,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1363,10 +1392,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Automated quality checks added/strengthened in this PR.</t>
+          <t>Automated quality so future changes don't silently break things.</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1439,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Asserts hotelier payloads never expose WhatsApp/SMTP/Razorpay/AI secrets</t>
+          <t>Hotelier payloads never expose secrets</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1437,12 +1466,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Pins the AI token-accounting math</t>
+          <t>AI token-accounting math</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Protects cost visibility from under-counting</t>
+          <t>Protects cost visibility</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1464,12 +1493,12 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Verifies the new fail-closed in-process AI cap (CH-07)</t>
+          <t>The new fail-closed AI cap</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Confirms cost protection during a Redis outage</t>
+          <t>Confirms cost protection in a Redis outage</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -1481,22 +1510,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>backend-ci.yml</t>
+          <t>test_limiter_ip.py</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Added coverage (pytest-cov) + pip-audit CVE scan + compile gate; runs on PRs</t>
+          <t>Trusted-proxy IP extraction</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Regressions &amp; vulnerable deps caught pre-merge</t>
+          <t>Confirms spoofed headers are ignored</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1508,22 +1537,22 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Backend suite</t>
+          <t>backend-ci.yml</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>265 passing, 1 skipped (+12 vs baseline)</t>
+          <t>coverage + pip-audit CVE scan + compile gate</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Broader safety net</t>
+          <t>Catches regressions &amp; vulnerable deps pre-merge</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -1535,25 +1564,52 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>Suite total</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>270 passing, 1 skipped (+17)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Broader safety net</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>tsc --noEmit clean + vite production build green</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>UI changes verified to compile &amp; build</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>tsc clean + vite build green</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>UI changes verified</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1569,6 +1625,700 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>4.  Errors Identified — full transparency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>We are not hiding anything: this is the honest list of issues found. Some are fixed in this PR; the rest are scheduled (see roadmap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Error / Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Fake calendar Sold-Out / prices</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Public booking</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Fixed (CH-01/02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>postMessage data leak</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AI widget</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Fixed (CH-03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Blank page on fetch failure</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Room selection</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Fixed (CH-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Missing date validation</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Fixed (CH-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Tax slab/rate not validated</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Fixed (CH-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Availability not status-indexed</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Fixed (CH-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>AI cost cap fail-open</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Fixed (CH-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Spoofable IP rate limit</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Fixed (CH-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>DB connection held during LLM call</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Backend/scale</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Redis single point of failure</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Rate limiting on authed routes</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Guests page renders all rows (no pagination)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Optimistic delete without rollback</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Currency hardcoded to INR</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Payment-verify failure reconciliation</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Reports/PDF generated in-request (memory)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Identified</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5.  Possible Future Errors — what may still go wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Honest, forward-looking risks that typically appear only under heavy production load. Shown with when, why, and how we will mitigate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Possible error</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>What guests/hotels would see</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>When it may occur</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Why it occurs</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Mitigation plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Connection pool exhaustion</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>API 500s for all hotels at once</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>During a big traffic spike (sale/campaign)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Pool too small + connections held during slow AI calls</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Right-size pool; release DB session before LLM; load test</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Database slows as data grows</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Slow search/reports</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>As hotels onboard and data reaches GBs</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Large tables + heavy/unindexed queries</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Indexes (started), read replicas, archive old data</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Redis outage</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Limits/cache/idempotency degrade</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>If the single Redis instance fails</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>No high-availability Redis yet</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Managed HA Redis; we already added fail-closed AI cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Booking race / overbooking</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Two guests get the last room</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Simultaneous bookings, same room/date</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Availability checked then booked non-atomically</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Atomic check + DB unique constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Third-party outage (Razorpay/AI/WhatsApp)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Payments/AI/notifications fail</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>On provider downtime or breaking change</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>External dependency with no SLA</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Timeouts, retries, fallbacks, status alerts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>AI cost grows with usage</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Higher monthly LLM bill</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>As more guests use the concierge</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Per-message model cost</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Budgets, caching, cheap models (done), auto-throttle</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>API abuse / DDoS</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Service degraded</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Targeted attack</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Public endpoints + (now hardened) IP limits</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>WAF/CDN; trusted-proxy IP (done); per-hotel quotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Worker memory spike</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Worker restarts, dropped requests</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Many report/PDF exports at once</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Heavy libs run in-request</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Move report generation to a background queue</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1586,14 +2336,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>4.  Remaining for full 1000+ readiness (honest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>6.  Remaining for full 1000+ readiness (honest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>What is NOT yet done. These are infra/architecture items scheduled next — kept transparent so status is accurate.</t>
+          <t>Not yet done — mostly infrastructure/ops items that need provisioning and load testing, not just code. Kept transparent so status is accurate.</t>
         </is>
       </c>
     </row>
@@ -1637,7 +2387,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Decouples AI concurrency from the DB pool</t>
+          <t>Decouples AI load from the DB pool</t>
         </is>
       </c>
     </row>
@@ -1654,7 +2404,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Infra/ops</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1666,12 +2416,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Trusted-proxy IP + rate-limit authed routes</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Rate-limit authenticated routes</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1681,7 +2431,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Hardens abuse/DoS resistance</t>
+          <t>Hardens abuse on logged-in endpoints</t>
         </is>
       </c>
     </row>
@@ -1698,7 +2448,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Infra/ops</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1732,7 +2482,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Taxes calculator div-by-zero; dashboard polish</t>
+          <t>Pagination + debounce on big lists</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -1747,14 +2497,14 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Dashboard correctness (separate from public funnel)</t>
+          <t>Smooth dashboards for large hotels</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Load test at peak + DB pool sizing</t>
+          <t>Load test at peak + pool sizing</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
